--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119782327</v>
+        <v>119782328</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788527</v>
+        <v>788523</v>
       </c>
       <c r="R3" t="n">
-        <v>7369670</v>
+        <v>7369769</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119782328</v>
+        <v>119782323</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788523</v>
+        <v>788556</v>
       </c>
       <c r="R4" t="n">
-        <v>7369769</v>
+        <v>7369628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119782326</v>
+        <v>119782329</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788527</v>
+        <v>788519</v>
       </c>
       <c r="R5" t="n">
-        <v>7369640</v>
+        <v>7369664</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119782324</v>
+        <v>119782326</v>
       </c>
       <c r="B6" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788510</v>
+        <v>788527</v>
       </c>
       <c r="R6" t="n">
-        <v>7369678</v>
+        <v>7369640</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119782323</v>
+        <v>119782327</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788556</v>
+        <v>788527</v>
       </c>
       <c r="R7" t="n">
-        <v>7369628</v>
+        <v>7369670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119782329</v>
+        <v>119782324</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788519</v>
+        <v>788510</v>
       </c>
       <c r="R8" t="n">
-        <v>7369664</v>
+        <v>7369678</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1415,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119782328</v>
+        <v>119782327</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788523</v>
+        <v>788527</v>
       </c>
       <c r="R3" t="n">
-        <v>7369769</v>
+        <v>7369670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119782329</v>
+        <v>119782326</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788519</v>
+        <v>788527</v>
       </c>
       <c r="R5" t="n">
-        <v>7369664</v>
+        <v>7369640</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119782326</v>
+        <v>119782328</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1159,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788527</v>
+        <v>788523</v>
       </c>
       <c r="R6" t="n">
-        <v>7369640</v>
+        <v>7369769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119782327</v>
+        <v>119782324</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788527</v>
+        <v>788510</v>
       </c>
       <c r="R7" t="n">
-        <v>7369670</v>
+        <v>7369678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119782324</v>
+        <v>119782329</v>
       </c>
       <c r="B8" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788510</v>
+        <v>788519</v>
       </c>
       <c r="R8" t="n">
-        <v>7369678</v>
+        <v>7369664</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1414,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119782327</v>
+        <v>119782328</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788527</v>
+        <v>788523</v>
       </c>
       <c r="R3" t="n">
-        <v>7369670</v>
+        <v>7369769</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119782323</v>
+        <v>119782329</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788556</v>
+        <v>788519</v>
       </c>
       <c r="R4" t="n">
-        <v>7369628</v>
+        <v>7369664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119782326</v>
+        <v>119782323</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788527</v>
+        <v>788556</v>
       </c>
       <c r="R5" t="n">
-        <v>7369640</v>
+        <v>7369628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119782328</v>
+        <v>119782324</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788523</v>
+        <v>788510</v>
       </c>
       <c r="R6" t="n">
-        <v>7369769</v>
+        <v>7369678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119782324</v>
+        <v>119782326</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788510</v>
+        <v>788527</v>
       </c>
       <c r="R7" t="n">
-        <v>7369678</v>
+        <v>7369640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119782329</v>
+        <v>119782327</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788519</v>
+        <v>788527</v>
       </c>
       <c r="R8" t="n">
-        <v>7369664</v>
+        <v>7369670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1415,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119782328</v>
+        <v>119782323</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788523</v>
+        <v>788556</v>
       </c>
       <c r="R3" t="n">
-        <v>7369769</v>
+        <v>7369628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119782329</v>
+        <v>119782327</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788519</v>
+        <v>788527</v>
       </c>
       <c r="R4" t="n">
-        <v>7369664</v>
+        <v>7369670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119782323</v>
+        <v>119782328</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788556</v>
+        <v>788523</v>
       </c>
       <c r="R5" t="n">
-        <v>7369628</v>
+        <v>7369769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119782324</v>
+        <v>119782326</v>
       </c>
       <c r="B6" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788510</v>
+        <v>788527</v>
       </c>
       <c r="R6" t="n">
-        <v>7369678</v>
+        <v>7369640</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119782326</v>
+        <v>119782324</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788527</v>
+        <v>788510</v>
       </c>
       <c r="R7" t="n">
-        <v>7369640</v>
+        <v>7369678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119782327</v>
+        <v>119782329</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788527</v>
+        <v>788519</v>
       </c>
       <c r="R8" t="n">
-        <v>7369670</v>
+        <v>7369664</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1414,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119782323</v>
+        <v>119782327</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788556</v>
+        <v>788527</v>
       </c>
       <c r="R3" t="n">
-        <v>7369628</v>
+        <v>7369670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119782327</v>
+        <v>119782329</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788527</v>
+        <v>788519</v>
       </c>
       <c r="R4" t="n">
-        <v>7369670</v>
+        <v>7369664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119782328</v>
+        <v>119782323</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788523</v>
+        <v>788556</v>
       </c>
       <c r="R5" t="n">
-        <v>7369769</v>
+        <v>7369628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119782326</v>
+        <v>119782324</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788527</v>
+        <v>788510</v>
       </c>
       <c r="R6" t="n">
-        <v>7369640</v>
+        <v>7369678</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119782324</v>
+        <v>119782326</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788510</v>
+        <v>788527</v>
       </c>
       <c r="R7" t="n">
-        <v>7369678</v>
+        <v>7369640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119782329</v>
+        <v>119782328</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788519</v>
+        <v>788523</v>
       </c>
       <c r="R8" t="n">
-        <v>7369664</v>
+        <v>7369769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1415,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1435,6 +1435,1436 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120595082</v>
+      </c>
+      <c r="B9" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>788439</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7369763</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120595089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>788439</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7369763</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120595093</v>
+      </c>
+      <c r="B11" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>788567</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7369614</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120595080</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87423</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>788675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7369632</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120595094</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>788701</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7369662</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120595095</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>788439</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7369763</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120595088</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74649</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>310</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>788435</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7369772</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120595086</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>788602</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7369575</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120595090</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>788545</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7369602</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120595083</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>788621</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7369589</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120595092</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>788436</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7369754</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120595091</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>788585</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7369713</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120595084</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>788738</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7369696</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120595087</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>788657</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7369604</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2865,6 +2865,972 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121409359</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>788549</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7369608</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121409369</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>788534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7369607</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121409372</v>
+      </c>
+      <c r="B25" t="n">
+        <v>82385</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>788557</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7369630</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121409371</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>788509</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7369641</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121409364</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57462</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>788417</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7369751</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121409363</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97041</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>788505</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7369652</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121409367</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90715</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>788520</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7369632</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121409370</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>788542</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7369608</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121409373</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82385</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>788454</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7369788</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409359</v>
+        <v>121409373</v>
       </c>
       <c r="B23" t="n">
-        <v>56563</v>
+        <v>82385</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,50 +2879,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788549</v>
+        <v>788454</v>
       </c>
       <c r="R23" t="n">
-        <v>7369608</v>
+        <v>7369788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409369</v>
+        <v>121409364</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3025,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788534</v>
+        <v>788417</v>
       </c>
       <c r="R24" t="n">
-        <v>7369607</v>
+        <v>7369751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409372</v>
+        <v>121409369</v>
       </c>
       <c r="B25" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788557</v>
+        <v>788534</v>
       </c>
       <c r="R25" t="n">
-        <v>7369630</v>
+        <v>7369607</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409371</v>
+        <v>121409372</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3201,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788509</v>
+        <v>788557</v>
       </c>
       <c r="R26" t="n">
-        <v>7369641</v>
+        <v>7369630</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409364</v>
+        <v>121409363</v>
       </c>
       <c r="B27" t="n">
-        <v>57462</v>
+        <v>97041</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,21 +3307,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3343,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788417</v>
+        <v>788505</v>
       </c>
       <c r="R27" t="n">
-        <v>7369751</v>
+        <v>7369652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409363</v>
+        <v>121409371</v>
       </c>
       <c r="B28" t="n">
-        <v>97041</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3421,25 +3409,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788505</v>
+        <v>788509</v>
       </c>
       <c r="R28" t="n">
-        <v>7369652</v>
+        <v>7369641</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409367</v>
+        <v>121409370</v>
       </c>
       <c r="B29" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788520</v>
+        <v>788542</v>
       </c>
       <c r="R29" t="n">
-        <v>7369632</v>
+        <v>7369608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409370</v>
+        <v>121409367</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3625,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788542</v>
+        <v>788520</v>
       </c>
       <c r="R30" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409373</v>
+        <v>121409359</v>
       </c>
       <c r="B31" t="n">
-        <v>82385</v>
+        <v>56563</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,38 +3727,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788454</v>
+        <v>788549</v>
       </c>
       <c r="R31" t="n">
-        <v>7369788</v>
+        <v>7369608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3185,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409372</v>
+        <v>121409363</v>
       </c>
       <c r="B26" t="n">
-        <v>82385</v>
+        <v>97041</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,25 +3197,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788557</v>
+        <v>788505</v>
       </c>
       <c r="R26" t="n">
-        <v>7369630</v>
+        <v>7369652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409363</v>
+        <v>121409372</v>
       </c>
       <c r="B27" t="n">
-        <v>97041</v>
+        <v>82385</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788505</v>
+        <v>788557</v>
       </c>
       <c r="R27" t="n">
-        <v>7369652</v>
+        <v>7369630</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409370</v>
+        <v>121409367</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788542</v>
+        <v>788520</v>
       </c>
       <c r="R29" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409367</v>
+        <v>121409370</v>
       </c>
       <c r="B30" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788520</v>
+        <v>788542</v>
       </c>
       <c r="R30" t="n">
-        <v>7369632</v>
+        <v>7369608</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>121409373</v>
       </c>
       <c r="B23" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409364</v>
+        <v>121409344</v>
       </c>
       <c r="B24" t="n">
-        <v>57462</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,38 +2985,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slätthedmyran, Nb</t>
+          <t>NB okänd, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788417</v>
+        <v>788534</v>
       </c>
       <c r="R24" t="n">
-        <v>7369751</v>
+        <v>7369607</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3073,16 +3073,16 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+          <t>copy DNA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409369</v>
+        <v>121409370</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788534</v>
+        <v>788542</v>
       </c>
       <c r="R25" t="n">
-        <v>7369607</v>
+        <v>7369608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409363</v>
+        <v>121409364</v>
       </c>
       <c r="B26" t="n">
-        <v>97041</v>
+        <v>57462</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788505</v>
+        <v>788417</v>
       </c>
       <c r="R26" t="n">
-        <v>7369652</v>
+        <v>7369751</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409372</v>
+        <v>121409363</v>
       </c>
       <c r="B27" t="n">
-        <v>82385</v>
+        <v>97054</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788557</v>
+        <v>788505</v>
       </c>
       <c r="R27" t="n">
-        <v>7369630</v>
+        <v>7369652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409371</v>
+        <v>121409372</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788509</v>
+        <v>788557</v>
       </c>
       <c r="R28" t="n">
-        <v>7369641</v>
+        <v>7369630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409367</v>
+        <v>121409371</v>
       </c>
       <c r="B29" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788520</v>
+        <v>788509</v>
       </c>
       <c r="R29" t="n">
-        <v>7369632</v>
+        <v>7369641</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409370</v>
+        <v>121409367</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3625,21 +3625,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788542</v>
+        <v>788520</v>
       </c>
       <c r="R30" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409373</v>
+        <v>121409370</v>
       </c>
       <c r="B23" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788454</v>
+        <v>788542</v>
       </c>
       <c r="R23" t="n">
-        <v>7369788</v>
+        <v>7369608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409344</v>
+        <v>121409367</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,34 +2989,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NB okänd, Nb</t>
+          <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788534</v>
+        <v>788520</v>
       </c>
       <c r="R24" t="n">
-        <v>7369607</v>
+        <v>7369632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3073,13 +3073,13 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>copy DNA</t>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409370</v>
+        <v>121409344</v>
       </c>
       <c r="B25" t="n">
         <v>78604</v>
@@ -3115,14 +3115,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slätthedmyran, Nb</t>
+          <t>NB okänd, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788542</v>
+        <v>788534</v>
       </c>
       <c r="R25" t="n">
-        <v>7369608</v>
+        <v>7369607</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,16 +3179,16 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+          <t>copy DNA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409364</v>
+        <v>121409363</v>
       </c>
       <c r="B26" t="n">
-        <v>57462</v>
+        <v>97055</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788417</v>
+        <v>788505</v>
       </c>
       <c r="R26" t="n">
-        <v>7369751</v>
+        <v>7369652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409363</v>
+        <v>121409359</v>
       </c>
       <c r="B27" t="n">
-        <v>97054</v>
+        <v>56563</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,34 +3307,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788505</v>
+        <v>788549</v>
       </c>
       <c r="R27" t="n">
-        <v>7369652</v>
+        <v>7369608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,7 +3409,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409372</v>
+        <v>121409373</v>
       </c>
       <c r="B28" t="n">
         <v>82388</v>
@@ -3437,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788557</v>
+        <v>788454</v>
       </c>
       <c r="R28" t="n">
-        <v>7369630</v>
+        <v>7369788</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409367</v>
+        <v>121409364</v>
       </c>
       <c r="B30" t="n">
-        <v>90727</v>
+        <v>57462</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788520</v>
+        <v>788417</v>
       </c>
       <c r="R30" t="n">
-        <v>7369632</v>
+        <v>7369751</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409359</v>
+        <v>121409372</v>
       </c>
       <c r="B31" t="n">
-        <v>56563</v>
+        <v>82388</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,50 +3739,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788549</v>
+        <v>788557</v>
       </c>
       <c r="R31" t="n">
-        <v>7369608</v>
+        <v>7369630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409370</v>
+        <v>121409363</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>97058</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788542</v>
+        <v>788505</v>
       </c>
       <c r="R23" t="n">
-        <v>7369608</v>
+        <v>7369652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409367</v>
+        <v>121409364</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>57465</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788520</v>
+        <v>788417</v>
       </c>
       <c r="R24" t="n">
-        <v>7369632</v>
+        <v>7369751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409344</v>
+        <v>121409371</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,14 +3115,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NB okänd, Nb</t>
+          <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788534</v>
+        <v>788509</v>
       </c>
       <c r="R25" t="n">
-        <v>7369607</v>
+        <v>7369641</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,16 +3179,16 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>copy DNA</t>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409363</v>
+        <v>121409367</v>
       </c>
       <c r="B26" t="n">
-        <v>97055</v>
+        <v>90731</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,25 +3197,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788505</v>
+        <v>788520</v>
       </c>
       <c r="R26" t="n">
-        <v>7369652</v>
+        <v>7369632</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409359</v>
+        <v>121409373</v>
       </c>
       <c r="B27" t="n">
-        <v>56563</v>
+        <v>82391</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,50 +3303,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788549</v>
+        <v>788454</v>
       </c>
       <c r="R27" t="n">
-        <v>7369608</v>
+        <v>7369788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409373</v>
+        <v>121409344</v>
       </c>
       <c r="B28" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,34 +3413,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slätthedmyran, Nb</t>
+          <t>NB okänd, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788454</v>
+        <v>788534</v>
       </c>
       <c r="R28" t="n">
-        <v>7369788</v>
+        <v>7369607</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3509,16 +3497,16 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+          <t>copy DNA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409371</v>
+        <v>121409359</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>56566</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,38 +3515,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788509</v>
+        <v>788549</v>
       </c>
       <c r="R29" t="n">
-        <v>7369641</v>
+        <v>7369608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409364</v>
+        <v>121409372</v>
       </c>
       <c r="B30" t="n">
-        <v>57462</v>
+        <v>82391</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788417</v>
+        <v>788557</v>
       </c>
       <c r="R30" t="n">
-        <v>7369751</v>
+        <v>7369630</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409372</v>
+        <v>121409370</v>
       </c>
       <c r="B31" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3743,21 +3743,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788557</v>
+        <v>788542</v>
       </c>
       <c r="R31" t="n">
-        <v>7369630</v>
+        <v>7369608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409363</v>
+        <v>121409364</v>
       </c>
       <c r="B23" t="n">
-        <v>97058</v>
+        <v>57465</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788505</v>
+        <v>788417</v>
       </c>
       <c r="R23" t="n">
-        <v>7369652</v>
+        <v>7369751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409364</v>
+        <v>121409373</v>
       </c>
       <c r="B24" t="n">
-        <v>57465</v>
+        <v>82391</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788417</v>
+        <v>788454</v>
       </c>
       <c r="R24" t="n">
-        <v>7369751</v>
+        <v>7369788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409371</v>
+        <v>121409359</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,38 +3091,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788509</v>
+        <v>788549</v>
       </c>
       <c r="R25" t="n">
-        <v>7369641</v>
+        <v>7369608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409367</v>
+        <v>121409363</v>
       </c>
       <c r="B26" t="n">
-        <v>90731</v>
+        <v>97058</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3225,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788520</v>
+        <v>788505</v>
       </c>
       <c r="R26" t="n">
-        <v>7369632</v>
+        <v>7369652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409373</v>
+        <v>121409371</v>
       </c>
       <c r="B27" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,21 +3319,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788454</v>
+        <v>788509</v>
       </c>
       <c r="R27" t="n">
-        <v>7369788</v>
+        <v>7369641</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409344</v>
+        <v>121409372</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,34 +3425,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NB okänd, Nb</t>
+          <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788534</v>
+        <v>788557</v>
       </c>
       <c r="R28" t="n">
-        <v>7369607</v>
+        <v>7369630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,16 +3509,16 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>copy DNA</t>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409359</v>
+        <v>121409370</v>
       </c>
       <c r="B29" t="n">
-        <v>56566</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,47 +3527,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788549</v>
+        <v>788542</v>
       </c>
       <c r="R29" t="n">
         <v>7369608</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409372</v>
+        <v>121409369</v>
       </c>
       <c r="B30" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3637,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788557</v>
+        <v>788534</v>
       </c>
       <c r="R30" t="n">
-        <v>7369630</v>
+        <v>7369607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409370</v>
+        <v>121409367</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3743,21 +3743,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788542</v>
+        <v>788520</v>
       </c>
       <c r="R31" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3409,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409372</v>
+        <v>121409370</v>
       </c>
       <c r="B28" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788557</v>
+        <v>788542</v>
       </c>
       <c r="R28" t="n">
-        <v>7369630</v>
+        <v>7369608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409370</v>
+        <v>121409372</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788542</v>
+        <v>788557</v>
       </c>
       <c r="R29" t="n">
-        <v>7369608</v>
+        <v>7369630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3409,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409370</v>
+        <v>121409372</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788542</v>
+        <v>788557</v>
       </c>
       <c r="R28" t="n">
-        <v>7369608</v>
+        <v>7369630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409372</v>
+        <v>121409370</v>
       </c>
       <c r="B29" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788557</v>
+        <v>788542</v>
       </c>
       <c r="R29" t="n">
-        <v>7369630</v>
+        <v>7369608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409364</v>
+        <v>121409372</v>
       </c>
       <c r="B23" t="n">
-        <v>57465</v>
+        <v>82392</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788417</v>
+        <v>788557</v>
       </c>
       <c r="R23" t="n">
-        <v>7369751</v>
+        <v>7369630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409373</v>
+        <v>121409371</v>
       </c>
       <c r="B24" t="n">
-        <v>82391</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,21 +2989,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788454</v>
+        <v>788509</v>
       </c>
       <c r="R24" t="n">
-        <v>7369788</v>
+        <v>7369641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409359</v>
+        <v>121409373</v>
       </c>
       <c r="B25" t="n">
-        <v>56566</v>
+        <v>82392</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,50 +3091,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788549</v>
+        <v>788454</v>
       </c>
       <c r="R25" t="n">
-        <v>7369608</v>
+        <v>7369788</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409363</v>
+        <v>121409369</v>
       </c>
       <c r="B26" t="n">
-        <v>97058</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,25 +3197,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788505</v>
+        <v>788534</v>
       </c>
       <c r="R26" t="n">
-        <v>7369652</v>
+        <v>7369607</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409371</v>
+        <v>121409370</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788509</v>
+        <v>788542</v>
       </c>
       <c r="R27" t="n">
-        <v>7369641</v>
+        <v>7369608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409372</v>
+        <v>121409364</v>
       </c>
       <c r="B28" t="n">
-        <v>82391</v>
+        <v>57466</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3421,25 +3409,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788557</v>
+        <v>788417</v>
       </c>
       <c r="R28" t="n">
-        <v>7369630</v>
+        <v>7369751</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409370</v>
+        <v>121409363</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>97064</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,25 +3515,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788542</v>
+        <v>788505</v>
       </c>
       <c r="R29" t="n">
-        <v>7369608</v>
+        <v>7369652</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409369</v>
+        <v>121409367</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3625,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788534</v>
+        <v>788520</v>
       </c>
       <c r="R30" t="n">
-        <v>7369607</v>
+        <v>7369632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409367</v>
+        <v>121409359</v>
       </c>
       <c r="B31" t="n">
-        <v>90731</v>
+        <v>56567</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,38 +3727,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788520</v>
+        <v>788549</v>
       </c>
       <c r="R31" t="n">
-        <v>7369632</v>
+        <v>7369608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409372</v>
+        <v>121409363</v>
       </c>
       <c r="B23" t="n">
-        <v>82392</v>
+        <v>97065</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788557</v>
+        <v>788505</v>
       </c>
       <c r="R23" t="n">
-        <v>7369630</v>
+        <v>7369652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409371</v>
+        <v>121409359</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,38 +2985,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788509</v>
+        <v>788549</v>
       </c>
       <c r="R24" t="n">
-        <v>7369641</v>
+        <v>7369608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409373</v>
+        <v>121409367</v>
       </c>
       <c r="B25" t="n">
-        <v>82392</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3095,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788454</v>
+        <v>788520</v>
       </c>
       <c r="R25" t="n">
-        <v>7369788</v>
+        <v>7369632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409369</v>
+        <v>121409371</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788534</v>
+        <v>788509</v>
       </c>
       <c r="R26" t="n">
-        <v>7369607</v>
+        <v>7369641</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409370</v>
+        <v>121409369</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788542</v>
+        <v>788534</v>
       </c>
       <c r="R27" t="n">
-        <v>7369608</v>
+        <v>7369607</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409364</v>
+        <v>121409370</v>
       </c>
       <c r="B28" t="n">
-        <v>57466</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,25 +3421,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788417</v>
+        <v>788542</v>
       </c>
       <c r="R28" t="n">
-        <v>7369751</v>
+        <v>7369608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409363</v>
+        <v>121409373</v>
       </c>
       <c r="B29" t="n">
-        <v>97064</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,25 +3527,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3543,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788505</v>
+        <v>788454</v>
       </c>
       <c r="R29" t="n">
-        <v>7369652</v>
+        <v>7369788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409367</v>
+        <v>121409364</v>
       </c>
       <c r="B30" t="n">
-        <v>90737</v>
+        <v>57467</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788520</v>
+        <v>788417</v>
       </c>
       <c r="R30" t="n">
-        <v>7369632</v>
+        <v>7369751</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409359</v>
+        <v>121409372</v>
       </c>
       <c r="B31" t="n">
-        <v>56567</v>
+        <v>82393</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,50 +3739,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788549</v>
+        <v>788557</v>
       </c>
       <c r="R31" t="n">
-        <v>7369608</v>
+        <v>7369630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409363</v>
+        <v>121409370</v>
       </c>
       <c r="B23" t="n">
-        <v>97065</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788505</v>
+        <v>788542</v>
       </c>
       <c r="R23" t="n">
-        <v>7369652</v>
+        <v>7369608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409359</v>
+        <v>121409373</v>
       </c>
       <c r="B24" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,50 +2985,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788549</v>
+        <v>788454</v>
       </c>
       <c r="R24" t="n">
-        <v>7369608</v>
+        <v>7369788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409367</v>
+        <v>121409372</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>82393</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3107,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788520</v>
+        <v>788557</v>
       </c>
       <c r="R25" t="n">
-        <v>7369632</v>
+        <v>7369630</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409371</v>
+        <v>121409359</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,38 +3197,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788509</v>
+        <v>788549</v>
       </c>
       <c r="R26" t="n">
-        <v>7369641</v>
+        <v>7369608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409369</v>
+        <v>121409344</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3339,7 +3339,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slätthedmyran, Nb</t>
+          <t>NB okänd, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -3403,16 +3403,16 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+          <t>copy DNA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409370</v>
+        <v>121409367</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788542</v>
+        <v>788520</v>
       </c>
       <c r="R28" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409373</v>
+        <v>121409371</v>
       </c>
       <c r="B29" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788454</v>
+        <v>788509</v>
       </c>
       <c r="R29" t="n">
-        <v>7369788</v>
+        <v>7369641</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409372</v>
+        <v>121409363</v>
       </c>
       <c r="B31" t="n">
-        <v>82393</v>
+        <v>97065</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788557</v>
+        <v>788505</v>
       </c>
       <c r="R31" t="n">
-        <v>7369630</v>
+        <v>7369652</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409370</v>
+        <v>121409363</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>97065</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788542</v>
+        <v>788505</v>
       </c>
       <c r="R23" t="n">
-        <v>7369608</v>
+        <v>7369652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409373</v>
+        <v>121409369</v>
       </c>
       <c r="B24" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,21 +2989,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788454</v>
+        <v>788534</v>
       </c>
       <c r="R24" t="n">
-        <v>7369788</v>
+        <v>7369607</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409372</v>
+        <v>121409359</v>
       </c>
       <c r="B25" t="n">
-        <v>82393</v>
+        <v>56568</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,38 +3091,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788557</v>
+        <v>788549</v>
       </c>
       <c r="R25" t="n">
-        <v>7369630</v>
+        <v>7369608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409359</v>
+        <v>121409367</v>
       </c>
       <c r="B26" t="n">
-        <v>56568</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,50 +3209,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788549</v>
+        <v>788520</v>
       </c>
       <c r="R26" t="n">
-        <v>7369608</v>
+        <v>7369632</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409344</v>
+        <v>121409364</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>57467</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,38 +3315,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NB okänd, Nb</t>
+          <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788534</v>
+        <v>788417</v>
       </c>
       <c r="R27" t="n">
-        <v>7369607</v>
+        <v>7369751</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,16 +3403,16 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>copy DNA</t>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409367</v>
+        <v>121409373</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>82393</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788520</v>
+        <v>788454</v>
       </c>
       <c r="R28" t="n">
-        <v>7369632</v>
+        <v>7369788</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409371</v>
+        <v>121409372</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3531,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788509</v>
+        <v>788557</v>
       </c>
       <c r="R29" t="n">
-        <v>7369641</v>
+        <v>7369630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409364</v>
+        <v>121409370</v>
       </c>
       <c r="B30" t="n">
-        <v>57467</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788417</v>
+        <v>788542</v>
       </c>
       <c r="R30" t="n">
-        <v>7369751</v>
+        <v>7369608</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409363</v>
+        <v>121409371</v>
       </c>
       <c r="B31" t="n">
-        <v>97065</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788505</v>
+        <v>788509</v>
       </c>
       <c r="R31" t="n">
-        <v>7369652</v>
+        <v>7369641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409363</v>
+        <v>121409367</v>
       </c>
       <c r="B23" t="n">
-        <v>97065</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788505</v>
+        <v>788520</v>
       </c>
       <c r="R23" t="n">
-        <v>7369652</v>
+        <v>7369632</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409369</v>
+        <v>121409363</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>97065</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788534</v>
+        <v>788505</v>
       </c>
       <c r="R24" t="n">
-        <v>7369607</v>
+        <v>7369652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409359</v>
+        <v>121409373</v>
       </c>
       <c r="B25" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,50 +3091,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788549</v>
+        <v>788454</v>
       </c>
       <c r="R25" t="n">
-        <v>7369608</v>
+        <v>7369788</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409367</v>
+        <v>121409369</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3201,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788520</v>
+        <v>788534</v>
       </c>
       <c r="R26" t="n">
-        <v>7369632</v>
+        <v>7369607</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409364</v>
+        <v>121409370</v>
       </c>
       <c r="B27" t="n">
-        <v>57467</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3315,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3343,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788417</v>
+        <v>788542</v>
       </c>
       <c r="R27" t="n">
-        <v>7369751</v>
+        <v>7369608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409373</v>
+        <v>121409371</v>
       </c>
       <c r="B28" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788454</v>
+        <v>788509</v>
       </c>
       <c r="R28" t="n">
-        <v>7369788</v>
+        <v>7369641</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121409372</v>
+        <v>121409364</v>
       </c>
       <c r="B29" t="n">
-        <v>82393</v>
+        <v>57467</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3527,25 +3515,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>788557</v>
+        <v>788417</v>
       </c>
       <c r="R29" t="n">
-        <v>7369630</v>
+        <v>7369751</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409370</v>
+        <v>121409359</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,35 +3621,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788542</v>
+        <v>788549</v>
       </c>
       <c r="R30" t="n">
         <v>7369608</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409371</v>
+        <v>121409372</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3743,21 +3743,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788509</v>
+        <v>788557</v>
       </c>
       <c r="R31" t="n">
-        <v>7369641</v>
+        <v>7369630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121409367</v>
+        <v>121409369</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>788520</v>
+        <v>788534</v>
       </c>
       <c r="R23" t="n">
-        <v>7369632</v>
+        <v>7369607</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121409363</v>
+        <v>121409367</v>
       </c>
       <c r="B24" t="n">
-        <v>97065</v>
+        <v>90746</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>788505</v>
+        <v>788520</v>
       </c>
       <c r="R24" t="n">
-        <v>7369652</v>
+        <v>7369632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121409373</v>
+        <v>121409370</v>
       </c>
       <c r="B25" t="n">
-        <v>82393</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>788454</v>
+        <v>788542</v>
       </c>
       <c r="R25" t="n">
-        <v>7369788</v>
+        <v>7369608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121409369</v>
+        <v>121409359</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>56569</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,38 +3197,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>788534</v>
+        <v>788549</v>
       </c>
       <c r="R26" t="n">
-        <v>7369607</v>
+        <v>7369608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121409370</v>
+        <v>121409372</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,21 +3319,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>788542</v>
+        <v>788557</v>
       </c>
       <c r="R27" t="n">
-        <v>7369608</v>
+        <v>7369630</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121409371</v>
+        <v>121409373</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>788509</v>
+        <v>788454</v>
       </c>
       <c r="R28" t="n">
-        <v>7369641</v>
+        <v>7369788</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,7 +3518,7 @@
         <v>121409364</v>
       </c>
       <c r="B29" t="n">
-        <v>57467</v>
+        <v>57468</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3609,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121409359</v>
+        <v>121409371</v>
       </c>
       <c r="B30" t="n">
-        <v>56568</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3621,50 +3633,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>788549</v>
+        <v>788509</v>
       </c>
       <c r="R30" t="n">
-        <v>7369608</v>
+        <v>7369641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121409372</v>
+        <v>121409363</v>
       </c>
       <c r="B31" t="n">
-        <v>82393</v>
+        <v>97073</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>788557</v>
+        <v>788505</v>
       </c>
       <c r="R31" t="n">
-        <v>7369630</v>
+        <v>7369652</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3831,6 +3831,1341 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125699652</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>788781</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7369768</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125699651</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>788739</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7369815</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125699649</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91162</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>788713</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7369776</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125699642</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>788444</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7369770</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125699627</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>788688</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7369737</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125699657</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>788727</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7369801</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125699656</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>788544</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7369684</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125699618</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91338</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>788715</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7369770</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125699634</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>788476</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7369788</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125699668</v>
+      </c>
+      <c r="B41" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>788670</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7369718</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125699641</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58001</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>788648</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7369588</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125699667</v>
+      </c>
+      <c r="B43" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>788751</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7369826</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125699647</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slätthedmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>788623</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7369734</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B43" t="n">
-        <v>91216</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R43" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>91216</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R44" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91392</v>
+        <v>91399</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B41" t="n">
-        <v>91238</v>
+        <v>56834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R41" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B42" t="n">
-        <v>56834</v>
+        <v>91245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R42" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>91223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R43" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>91216</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R44" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3836,7 +3836,7 @@
         <v>125699641</v>
       </c>
       <c r="B32" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>125699668</v>
       </c>
       <c r="B35" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125699656</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>125699667</v>
       </c>
       <c r="B39" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B41" t="n">
-        <v>56834</v>
+        <v>91246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R41" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B42" t="n">
-        <v>91245</v>
+        <v>56834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R42" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4912,7 +4912,7 @@
         <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91403</v>
+        <v>91407</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>125699668</v>
       </c>
       <c r="B35" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125699656</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>125699667</v>
       </c>
       <c r="B39" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B41" t="n">
-        <v>91246</v>
+        <v>56834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R41" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B42" t="n">
-        <v>56834</v>
+        <v>91250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R42" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4912,7 +4912,7 @@
         <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B41" t="n">
-        <v>56834</v>
+        <v>91250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R41" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B42" t="n">
-        <v>91250</v>
+        <v>56834</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R42" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B43" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R43" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>91228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R44" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3836,7 +3836,7 @@
         <v>125699641</v>
       </c>
       <c r="B32" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>125699668</v>
       </c>
       <c r="B35" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>125699634</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125699656</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>125699642</v>
       </c>
       <c r="B38" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>125699667</v>
       </c>
       <c r="B39" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>125699627</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>125699651</v>
       </c>
       <c r="B41" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125699647</v>
       </c>
       <c r="B42" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>125699657</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>125699649</v>
       </c>
       <c r="B44" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>91230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R43" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>91230</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R44" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91409</v>
+        <v>91411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B41" t="n">
-        <v>91252</v>
+        <v>56835</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R41" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B42" t="n">
-        <v>56835</v>
+        <v>91254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R42" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B43" t="n">
-        <v>91230</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R43" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>91232</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R44" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91411</v>
+        <v>91413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B41" t="n">
-        <v>56835</v>
+        <v>91256</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R41" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B42" t="n">
-        <v>91254</v>
+        <v>56835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R42" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125699657</v>
+        <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>91234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>788727</v>
+        <v>788713</v>
       </c>
       <c r="R43" t="n">
-        <v>7369801</v>
+        <v>7369776</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125699649</v>
+        <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>788713</v>
+        <v>788727</v>
       </c>
       <c r="R44" t="n">
-        <v>7369776</v>
+        <v>7369801</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -3836,7 +3836,7 @@
         <v>125699641</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>125699652</v>
       </c>
       <c r="B33" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>125699618</v>
       </c>
       <c r="B34" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>125699668</v>
       </c>
       <c r="B35" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>125699634</v>
       </c>
       <c r="B36" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>125699656</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>125699642</v>
       </c>
       <c r="B38" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>125699667</v>
       </c>
       <c r="B39" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>125699627</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>125699651</v>
       </c>
       <c r="B41" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125699647</v>
       </c>
       <c r="B42" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>125699649</v>
       </c>
       <c r="B43" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>125699657</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50504-2023 artfynd.xlsx
+++ b/artfynd/A 50504-2023 artfynd.xlsx
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125699651</v>
+        <v>125699647</v>
       </c>
       <c r="B41" t="n">
-        <v>91260</v>
+        <v>56839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>788739</v>
+        <v>788623</v>
       </c>
       <c r="R41" t="n">
-        <v>7369815</v>
+        <v>7369734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125699647</v>
+        <v>125699651</v>
       </c>
       <c r="B42" t="n">
-        <v>56839</v>
+        <v>91260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>788623</v>
+        <v>788739</v>
       </c>
       <c r="R42" t="n">
-        <v>7369734</v>
+        <v>7369815</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
